--- a/normalData.xlsx
+++ b/normalData.xlsx
@@ -5,18 +5,23 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EBCD3A-AF6E-41D0-A244-2104BC990A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2EB797-4B15-444D-9411-CD36CFFB8F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="861" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
     <sheet name="editButton" sheetId="2" r:id="rId2"/>
-    <sheet name="career_match" sheetId="12" r:id="rId3"/>
-    <sheet name="education_match" sheetId="13" r:id="rId4"/>
+    <sheet name="education_match" sheetId="13" r:id="rId3"/>
+    <sheet name="career_match" sheetId="12" r:id="rId4"/>
+    <sheet name="location_match" sheetId="14" r:id="rId5"/>
+    <sheet name="career_classify" sheetId="15" r:id="rId6"/>
+    <sheet name="education_classify" sheetId="16" r:id="rId7"/>
+    <sheet name="location_classify" sheetId="17" r:id="rId8"/>
+    <sheet name="career_card" sheetId="19" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="410">
   <si>
     <t>activeScence</t>
   </si>
@@ -193,10 +198,6 @@
     <t>數學</t>
   </si>
   <si>
-    <t>building_classify</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>building_card</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -573,9 +574,6 @@
     <t>幫派成員</t>
   </si>
   <si>
-    <t>instructor</t>
-  </si>
-  <si>
     <t>教師</t>
   </si>
   <si>
@@ -805,9 +803,6 @@
     <t>建設</t>
   </si>
   <si>
-    <t>context</t>
-  </si>
-  <si>
     <t>背景</t>
   </si>
   <si>
@@ -823,179 +818,517 @@
     <t>經濟學</t>
   </si>
   <si>
-    <t>engineering</t>
-  </si>
-  <si>
-    <t>工程</t>
-  </si>
-  <si>
     <t>essay</t>
   </si>
   <si>
     <t>散文</t>
   </si>
   <si>
+    <t>解釋</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>公式</t>
+  </si>
+  <si>
+    <t>grammar</t>
+  </si>
+  <si>
+    <t>文法</t>
+  </si>
+  <si>
+    <t>grammatical</t>
+  </si>
+  <si>
+    <t>文法的</t>
+  </si>
+  <si>
+    <t>idiom</t>
+  </si>
+  <si>
+    <t>慣用語</t>
+  </si>
+  <si>
+    <t>informative</t>
+  </si>
+  <si>
+    <t>資訊豐富的</t>
+  </si>
+  <si>
+    <t>initial</t>
+  </si>
+  <si>
+    <t>最初的</t>
+  </si>
+  <si>
+    <t>intellectual</t>
+  </si>
+  <si>
+    <t>知識分子</t>
+  </si>
+  <si>
+    <t>intelligence</t>
+  </si>
+  <si>
+    <t>智慧</t>
+  </si>
+  <si>
+    <t>intermediate</t>
+  </si>
+  <si>
+    <t>中級的</t>
+  </si>
+  <si>
+    <t>intonation</t>
+  </si>
+  <si>
+    <t>語調</t>
+  </si>
+  <si>
+    <t>lecture</t>
+  </si>
+  <si>
+    <t>演講</t>
+  </si>
+  <si>
+    <t>literary</t>
+  </si>
+  <si>
+    <t>文學的</t>
+  </si>
+  <si>
+    <t>literature</t>
+  </si>
+  <si>
+    <t>文學</t>
+  </si>
+  <si>
+    <t>logic</t>
+  </si>
+  <si>
+    <t>邏輯</t>
+  </si>
+  <si>
+    <t>objective</t>
+  </si>
+  <si>
+    <t>目標；客觀的</t>
+  </si>
+  <si>
+    <t>paragraph</t>
+  </si>
+  <si>
+    <t>段落</t>
+  </si>
+  <si>
+    <t>philosophy</t>
+  </si>
+  <si>
+    <t>哲學</t>
+  </si>
+  <si>
+    <t>physics</t>
+  </si>
+  <si>
+    <t>物理學</t>
+  </si>
+  <si>
+    <t>psychology</t>
+  </si>
+  <si>
+    <t>心理學</t>
+  </si>
+  <si>
+    <t>alley</t>
+  </si>
+  <si>
+    <t>小巷</t>
+  </si>
+  <si>
+    <t>avenue</t>
+  </si>
+  <si>
+    <t>大道</t>
+  </si>
+  <si>
+    <t>barn</t>
+  </si>
+  <si>
+    <t>穀倉</t>
+  </si>
+  <si>
+    <t>cabin</t>
+  </si>
+  <si>
+    <t>小木屋</t>
+  </si>
+  <si>
+    <t>campus</t>
+  </si>
+  <si>
+    <t>校園</t>
+  </si>
+  <si>
+    <t>chimney</t>
+  </si>
+  <si>
+    <t>煙囪</t>
+  </si>
+  <si>
+    <t>circus</t>
+  </si>
+  <si>
+    <t>馬戲團</t>
+  </si>
+  <si>
+    <t>clinic</t>
+  </si>
+  <si>
+    <t>診所</t>
+  </si>
+  <si>
+    <t>college</t>
+  </si>
+  <si>
+    <t>學院</t>
+  </si>
+  <si>
+    <t>dam</t>
+  </si>
+  <si>
+    <t>水壩</t>
+  </si>
+  <si>
+    <t>dock</t>
+  </si>
+  <si>
+    <t>碼頭</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>壕溝</t>
+  </si>
+  <si>
+    <t>gym</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>體育館</t>
+  </si>
+  <si>
+    <t>harbor</t>
+  </si>
+  <si>
+    <t>港口</t>
+  </si>
+  <si>
+    <t>headquarters</t>
+  </si>
+  <si>
+    <t>總部</t>
+  </si>
+  <si>
+    <t>hometown</t>
+  </si>
+  <si>
+    <t>家鄉</t>
+  </si>
+  <si>
+    <t>hut</t>
+  </si>
+  <si>
+    <t>小屋</t>
+  </si>
+  <si>
+    <t>inn</t>
+  </si>
+  <si>
+    <t>小旅館</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>監獄</t>
+  </si>
+  <si>
+    <t>lobby</t>
+  </si>
+  <si>
+    <t>大廳</t>
+  </si>
+  <si>
+    <t>燈塔</t>
+  </si>
+  <si>
+    <t>mall</t>
+  </si>
+  <si>
+    <t>購物中心</t>
+  </si>
+  <si>
+    <t>motel</t>
+  </si>
+  <si>
+    <t>汽車旅館</t>
+  </si>
+  <si>
+    <t>palace</t>
+  </si>
+  <si>
+    <t>宮殿</t>
+  </si>
+  <si>
+    <t>paradise</t>
+  </si>
+  <si>
+    <t>天堂</t>
+  </si>
+  <si>
+    <t>pub</t>
+  </si>
+  <si>
+    <t>酒吧</t>
+  </si>
+  <si>
+    <t>skyscraper</t>
+  </si>
+  <si>
+    <t>摩天大樓</t>
+  </si>
+  <si>
+    <t>stadium</t>
+  </si>
+  <si>
+    <t>體育場</t>
+  </si>
+  <si>
+    <t>studio</t>
+  </si>
+  <si>
+    <t>工作室</t>
+  </si>
+  <si>
+    <t>cinema</t>
+  </si>
+  <si>
+    <t>電影院</t>
+  </si>
+  <si>
+    <t>cliff</t>
+  </si>
+  <si>
+    <t>懸崖</t>
+  </si>
+  <si>
+    <t>cottage</t>
+  </si>
+  <si>
+    <t>dormitory / dorm</t>
+  </si>
+  <si>
+    <t>宿舍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>embassy</t>
+  </si>
+  <si>
+    <t>大使館</t>
+  </si>
+  <si>
+    <t>freeway</t>
+  </si>
+  <si>
+    <t>高速公路</t>
+  </si>
+  <si>
+    <t>hostel</t>
+  </si>
+  <si>
+    <t>青年旅館</t>
+  </si>
+  <si>
+    <t>laboratory / lab</t>
+  </si>
+  <si>
+    <t>實驗室</t>
+  </si>
+  <si>
+    <t>locker</t>
+  </si>
+  <si>
+    <t>儲物櫃</t>
+  </si>
+  <si>
+    <t>托兒所</t>
+  </si>
+  <si>
+    <t>athlete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>explanation</t>
-  </si>
-  <si>
-    <t>解釋</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>公式</t>
-  </si>
-  <si>
-    <t>grammar</t>
-  </si>
-  <si>
-    <t>文法</t>
-  </si>
-  <si>
-    <t>grammatical</t>
-  </si>
-  <si>
-    <t>文法的</t>
-  </si>
-  <si>
-    <t>idiom</t>
-  </si>
-  <si>
-    <t>慣用語</t>
-  </si>
-  <si>
-    <t>illustration</t>
-  </si>
-  <si>
-    <t>插畫</t>
-  </si>
-  <si>
-    <t>informative</t>
-  </si>
-  <si>
-    <t>資訊豐富的</t>
-  </si>
-  <si>
-    <t>initial</t>
-  </si>
-  <si>
-    <t>最初的</t>
-  </si>
-  <si>
-    <t>intellectual</t>
-  </si>
-  <si>
-    <t>知識分子</t>
-  </si>
-  <si>
-    <t>intelligence</t>
-  </si>
-  <si>
-    <t>智慧</t>
-  </si>
-  <si>
-    <t>intermediate</t>
-  </si>
-  <si>
-    <t>中級的</t>
-  </si>
-  <si>
-    <t>intonation</t>
-  </si>
-  <si>
-    <t>語調</t>
-  </si>
-  <si>
-    <t>learning</t>
-  </si>
-  <si>
-    <t>學習</t>
-  </si>
-  <si>
-    <t>lecture</t>
-  </si>
-  <si>
-    <t>演講</t>
-  </si>
-  <si>
-    <t>literary</t>
-  </si>
-  <si>
-    <t>文學的</t>
-  </si>
-  <si>
-    <t>literature</t>
-  </si>
-  <si>
-    <t>文學</t>
-  </si>
-  <si>
-    <t>logic</t>
-  </si>
-  <si>
-    <t>邏輯</t>
-  </si>
-  <si>
-    <t>objective</t>
-  </si>
-  <si>
-    <t>目標；客觀的</t>
-  </si>
-  <si>
-    <t>paragraph</t>
-  </si>
-  <si>
-    <t>段落</t>
-  </si>
-  <si>
-    <t>percent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>百分之…</t>
-  </si>
-  <si>
-    <t>percentage</t>
-  </si>
-  <si>
-    <t>百分比</t>
-  </si>
-  <si>
-    <t>philosophy</t>
-  </si>
-  <si>
-    <t>哲學</t>
-  </si>
-  <si>
-    <t>physics</t>
-  </si>
-  <si>
-    <t>物理學</t>
-  </si>
-  <si>
-    <t>pronunciation</t>
-  </si>
-  <si>
-    <t>發音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正確答案:Kind of career</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>錯誤答案:Not a Kind of career</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正確答案:Related to education or writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正確答案:unrelated to education or writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nursery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正確答案:kind of location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>錯誤答案:Not a Kind of location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>campus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lighthouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>psychology</t>
-  </si>
-  <si>
-    <t>心理學</t>
-  </si>
-  <si>
-    <t>quotation</t>
-  </si>
-  <si>
-    <t>引用</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>參考</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>career_classify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barber</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>guard</t>
+  </si>
+  <si>
+    <t>musician</t>
+  </si>
+  <si>
+    <t>pianist</t>
+  </si>
+  <si>
+    <t>Who would most likely analyze the causes of inflation in a country’s economy?</t>
+  </si>
+  <si>
+    <t>Which person would translate a book from English into Japanese?</t>
+  </si>
+  <si>
+    <t>Who is responsible for repairing complex electronic circuits?</t>
+  </si>
+  <si>
+    <t>journalist</t>
+  </si>
+  <si>
+    <t>Which person studies the behavior and emotions of human beings?</t>
+  </si>
+  <si>
+    <t>architect</t>
+  </si>
+  <si>
+    <t>Who would be hired to investigate a mysterious crime scene?</t>
+  </si>
+  <si>
+    <t>lawyer</t>
+  </si>
+  <si>
+    <t>Which professional creates melodies and harmonies for orchestras?</t>
+  </si>
+  <si>
+    <t>Who might deliver a lecture on quantum mechanics at a university?</t>
+  </si>
+  <si>
+    <t>Which expert would study the ideas of Aristotle and Socrates?</t>
+  </si>
+  <si>
+    <t>Who would diagnose diseases and perform surgery in a hospital?</t>
+  </si>
+  <si>
+    <t>Which person would organize a country’s diplomatic relations with others?</t>
+  </si>
+  <si>
+    <t>Who would design a new smartphone interface or fashion line?</t>
+  </si>
+  <si>
+    <t>Which person researches human behavior for scientific understanding?</t>
+  </si>
+  <si>
+    <t>Who ensures the safety of swimmers at the beach?</t>
+  </si>
+  <si>
+    <t>Which person is trained to fly airplanes safely through the sky?</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Who would build wooden furniture and repair doors?</t>
+  </si>
+  <si>
+    <t>Which professional writes novels that explore social issues?</t>
+  </si>
+  <si>
+    <t>Who would be in charge of managing a company’s overall operation?</t>
+  </si>
+  <si>
+    <t>Which person studies ancient civilizations and interprets past events?</t>
+  </si>
+  <si>
+    <t>Who would provide beauty services such as cutting or styling hair?</t>
+  </si>
+  <si>
+    <t>Which person investigates mental health and counsels patients?</t>
+  </si>
+  <si>
+    <t>editor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instructor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salesman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>career_card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1045,7 +1378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1055,6 +1388,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1399,7 +1736,7 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -1413,7 +1750,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>375</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
@@ -1427,7 +1764,7 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s">
         <v>38</v>
@@ -1441,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1455,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
@@ -1714,6 +2051,470 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D57D8C-95C2-4DBD-AE75-10E382385048}">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E98AFF-E280-424F-B2C7-103782CACFE5}">
   <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1747,10 +2548,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1758,10 +2559,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1769,10 +2570,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1780,10 +2581,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1791,10 +2592,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1802,10 +2603,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1813,10 +2614,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1824,10 +2625,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1835,10 +2636,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1846,10 +2647,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1857,10 +2658,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1868,10 +2669,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1879,10 +2680,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1890,10 +2691,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1901,10 +2702,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1912,10 +2713,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1923,10 +2724,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1934,10 +2735,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1945,10 +2746,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1956,10 +2757,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1967,10 +2768,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1978,10 +2779,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1989,10 +2790,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2000,10 +2801,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2011,10 +2812,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2022,10 +2823,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2033,10 +2834,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2044,10 +2845,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2055,10 +2856,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2066,10 +2867,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2077,10 +2878,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2088,10 +2889,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2099,10 +2900,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2110,10 +2911,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2121,10 +2922,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2132,10 +2933,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -2143,10 +2944,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2154,10 +2955,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -2165,10 +2966,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -2176,10 +2977,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -2187,10 +2988,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -2198,10 +2999,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2209,10 +3010,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -2220,10 +3021,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -2231,10 +3032,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -2242,10 +3043,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2253,10 +3054,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2264,10 +3065,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2275,10 +3076,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -2286,10 +3087,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2297,10 +3098,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2308,10 +3109,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -2319,10 +3120,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -2330,10 +3131,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -2341,10 +3142,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -2352,10 +3153,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2363,10 +3164,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -2374,10 +3175,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -2385,10 +3186,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2396,10 +3197,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -2407,10 +3208,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -2418,10 +3219,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>169</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -2429,10 +3230,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -2440,10 +3241,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -2451,10 +3252,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -2462,10 +3263,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -2473,10 +3274,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -2484,10 +3285,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -2495,10 +3296,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -2506,10 +3307,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -2517,10 +3318,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -2528,10 +3329,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -2539,10 +3340,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -2550,10 +3351,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -2561,10 +3362,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -2572,10 +3373,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -2583,10 +3384,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -2594,10 +3395,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -2605,10 +3406,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -2616,10 +3417,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -2627,10 +3428,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -2638,10 +3439,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2651,13 +3452,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D57D8C-95C2-4DBD-AE75-10E382385048}">
-  <dimension ref="A1:F49"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F36FC6-E45B-4788-B2F1-312BCA24C78F}">
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -2685,10 +3486,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2696,10 +3497,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>215</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2707,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2718,10 +3519,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>291</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2729,10 +3530,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>220</v>
+        <v>293</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>221</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2740,10 +3541,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>223</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2751,10 +3552,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2762,10 +3563,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>225</v>
+        <v>299</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2773,10 +3574,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>227</v>
+        <v>301</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2784,10 +3585,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2795,10 +3596,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2806,10 +3607,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>233</v>
+        <v>307</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2817,10 +3618,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>235</v>
+        <v>309</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>236</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2828,10 +3629,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>238</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2839,10 +3640,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2850,10 +3651,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>242</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2861,10 +3662,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>243</v>
+        <v>317</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>244</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2872,10 +3673,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>246</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2883,10 +3684,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>247</v>
+        <v>321</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>248</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2894,10 +3695,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2905,10 +3706,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2916,10 +3717,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>253</v>
+        <v>373</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>254</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2927,10 +3728,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2938,10 +3739,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2949,10 +3750,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2960,10 +3761,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2971,10 +3772,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>264</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2982,10 +3783,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>265</v>
+        <v>338</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>266</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2993,10 +3794,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -3004,10 +3805,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>270</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -3015,10 +3816,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>271</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -3026,10 +3827,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>273</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -3037,10 +3838,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>275</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -3048,10 +3849,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>278</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -3059,10 +3860,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>280</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -3070,10 +3871,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>282</v>
+        <v>354</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -3081,10 +3882,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>283</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -3092,10 +3893,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>286</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -3103,10 +3904,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>287</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>288</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -3114,98 +3915,1153 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FEA9D1-1FA3-43FD-B675-249F6B023CA8}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="46.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>365</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4A4946-9FF4-45CE-B08A-FAD5E392DA10}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>367</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F25273-3E8A-4823-9F35-B718A4ABA0B4}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="47.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>306</v>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>370</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>370</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37FF283F-D917-4A57-8A53-99A7E024B89B}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="33.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B21" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
